--- a/data/processed/positivacao/2021-12_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2021-12_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -24607,7 +24607,7 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B934" t="inlineStr"/>
@@ -36245,7 +36245,7 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr"/>
@@ -65059,7 +65059,7 @@
     <row r="2491">
       <c r="A2491" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2491" t="inlineStr"/>
@@ -66730,12 +66730,12 @@
       <c r="A2556" t="inlineStr"/>
       <c r="B2556" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 0 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 0,00
+          <t>Vendedor 1 - VENDEDOR 01: positivou 0 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 0,00
 Vendedor 18 - LOJA: positivou 75 cliente(s), não positivou 760 cliente(s) - Total vendido: R$ 84.617,67
-Vendedor 3 - FERNANDA: positivou 107 cliente(s), não positivou 340 cliente(s) - Total vendido: R$ 109.581,95
-Vendedor 4 - DANIELA: positivou 0 cliente(s), não positivou 649 cliente(s) - Total vendido: R$ 0,00
+Vendedor 3 - VENDEDOR 03: positivou 107 cliente(s), não positivou 340 cliente(s) - Total vendido: R$ 109.581,95
+Vendedor 4 - VENDEDOR 04: positivou 0 cliente(s), não positivou 649 cliente(s) - Total vendido: R$ 0,00
 Vendedor 5 - SITE: positivou 12 cliente(s), não positivou 446 cliente(s) - Total vendido: R$ 1.902,19
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2556" t="inlineStr"/>
